--- a/data/prices.xlsx
+++ b/data/prices.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7650DA0-D39E-4C0C-BA2E-503364D4308D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A62548-6714-496C-8BD3-980B684A99B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -659,7 +659,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -668,13 +668,13 @@
         <v>9</v>
       </c>
       <c r="E2" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F2" s="2">
         <v>0.05</v>
       </c>
       <c r="G2" s="3">
-        <v>1.244</v>
+        <v>1.2869999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -682,7 +682,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -691,13 +691,13 @@
         <v>11</v>
       </c>
       <c r="E3" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F3" s="2">
         <v>0.03</v>
       </c>
       <c r="G3" s="3">
-        <v>1.1779999999999999</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -705,7 +705,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -714,13 +714,13 @@
         <v>9</v>
       </c>
       <c r="E4" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F4" s="2">
         <v>0.05</v>
       </c>
       <c r="G4" s="3">
-        <v>1.244</v>
+        <v>1.2869999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -728,7 +728,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -737,13 +737,13 @@
         <v>11</v>
       </c>
       <c r="E5" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F5" s="2">
         <v>0.03</v>
       </c>
       <c r="G5" s="3">
-        <v>1.1779999999999999</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -751,7 +751,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>
@@ -760,13 +760,13 @@
         <v>9</v>
       </c>
       <c r="E6" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F6" s="2">
         <v>0.06</v>
       </c>
       <c r="G6" s="3">
-        <v>1.254</v>
+        <v>1.2969999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -774,7 +774,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -783,13 +783,13 @@
         <v>11</v>
       </c>
       <c r="E7" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F7" s="2">
         <v>0.04</v>
       </c>
       <c r="G7" s="3">
-        <v>1.1879999999999999</v>
+        <v>1.238</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -797,7 +797,7 @@
         <v>18</v>
       </c>
       <c r="B8" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
@@ -806,13 +806,13 @@
         <v>9</v>
       </c>
       <c r="E8" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F8" s="2">
         <v>0.06</v>
       </c>
       <c r="G8" s="3">
-        <v>1.254</v>
+        <v>1.2969999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -820,7 +820,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -829,13 +829,13 @@
         <v>11</v>
       </c>
       <c r="E9" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F9" s="2">
         <v>0.04</v>
       </c>
       <c r="G9" s="3">
-        <v>1.1879999999999999</v>
+        <v>1.238</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -843,7 +843,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C10" t="s">
         <v>22</v>
@@ -852,13 +852,13 @@
         <v>9</v>
       </c>
       <c r="E10" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F10" s="2">
         <v>0.11</v>
       </c>
       <c r="G10" s="3">
-        <v>1.304</v>
+        <v>1.347</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -866,7 +866,7 @@
         <v>23</v>
       </c>
       <c r="B11" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
@@ -875,13 +875,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F11" s="2">
         <v>0.05</v>
       </c>
       <c r="G11" s="3">
-        <v>1.244</v>
+        <v>1.2869999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -889,7 +889,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
@@ -898,13 +898,13 @@
         <v>11</v>
       </c>
       <c r="E12" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F12" s="2">
         <v>0.03</v>
       </c>
       <c r="G12" s="3">
-        <v>1.1779999999999999</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -912,7 +912,7 @@
         <v>26</v>
       </c>
       <c r="B13" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -921,13 +921,13 @@
         <v>9</v>
       </c>
       <c r="E13" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F13" s="2">
         <v>0.08</v>
       </c>
       <c r="G13" s="3">
-        <v>1.274</v>
+        <v>1.3169999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -935,7 +935,7 @@
         <v>28</v>
       </c>
       <c r="B14" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
@@ -944,13 +944,13 @@
         <v>11</v>
       </c>
       <c r="E14" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F14" s="2">
         <v>0.04</v>
       </c>
       <c r="G14" s="3">
-        <v>1.1879999999999999</v>
+        <v>1.238</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -958,7 +958,7 @@
         <v>29</v>
       </c>
       <c r="B15" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C15" t="s">
         <v>30</v>
@@ -967,13 +967,13 @@
         <v>9</v>
       </c>
       <c r="E15" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F15" s="2">
         <v>0.08</v>
       </c>
       <c r="G15" s="3">
-        <v>1.274</v>
+        <v>1.3169999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -981,7 +981,7 @@
         <v>31</v>
       </c>
       <c r="B16" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
@@ -990,13 +990,13 @@
         <v>11</v>
       </c>
       <c r="E16" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F16" s="2">
         <v>0.04</v>
       </c>
       <c r="G16" s="3">
-        <v>1.1879999999999999</v>
+        <v>1.238</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1004,7 +1004,7 @@
         <v>32</v>
       </c>
       <c r="B17" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
@@ -1013,13 +1013,13 @@
         <v>9</v>
       </c>
       <c r="E17" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F17" s="2">
         <v>0.08</v>
       </c>
       <c r="G17" s="3">
-        <v>1.274</v>
+        <v>1.3169999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1027,7 +1027,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C18" t="s">
         <v>33</v>
@@ -1036,13 +1036,13 @@
         <v>11</v>
       </c>
       <c r="E18" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F18" s="2">
         <v>0.04</v>
       </c>
       <c r="G18" s="3">
-        <v>1.1879999999999999</v>
+        <v>1.238</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1050,7 +1050,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C19" t="s">
         <v>36</v>
@@ -1059,13 +1059,13 @@
         <v>9</v>
       </c>
       <c r="E19" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F19" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G19" s="3">
-        <v>1.264</v>
+        <v>1.3069999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1073,7 +1073,7 @@
         <v>37</v>
       </c>
       <c r="B20" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
@@ -1082,13 +1082,13 @@
         <v>38</v>
       </c>
       <c r="E20" s="2">
-        <v>1.3180000000000001</v>
+        <v>1.3280000000000001</v>
       </c>
       <c r="F20" s="2">
         <v>0.09</v>
       </c>
       <c r="G20" s="3">
-        <v>1.4079999999999999</v>
+        <v>1.4179999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1096,7 +1096,7 @@
         <v>39</v>
       </c>
       <c r="B21" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
@@ -1105,13 +1105,13 @@
         <v>11</v>
       </c>
       <c r="E21" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F21" s="2">
         <v>0.03</v>
       </c>
       <c r="G21" s="3">
-        <v>1.1779999999999999</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1119,7 +1119,7 @@
         <v>40</v>
       </c>
       <c r="B22" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
@@ -1128,13 +1128,13 @@
         <v>41</v>
       </c>
       <c r="E22" s="2">
-        <v>1.385</v>
+        <v>1.4279999999999999</v>
       </c>
       <c r="F22" s="2">
         <v>0.09</v>
       </c>
       <c r="G22" s="3">
-        <v>1.4750000000000001</v>
+        <v>1.518</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1142,7 +1142,7 @@
         <v>42</v>
       </c>
       <c r="B23" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C23" t="s">
         <v>43</v>
@@ -1151,13 +1151,13 @@
         <v>9</v>
       </c>
       <c r="E23" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F23" s="2">
         <v>0.06</v>
       </c>
       <c r="G23" s="3">
-        <v>1.254</v>
+        <v>1.2969999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1165,7 +1165,7 @@
         <v>44</v>
       </c>
       <c r="B24" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C24" t="s">
         <v>43</v>
@@ -1174,13 +1174,13 @@
         <v>38</v>
       </c>
       <c r="E24" s="2">
-        <v>1.3180000000000001</v>
+        <v>1.3280000000000001</v>
       </c>
       <c r="F24" s="2">
         <v>0.08</v>
       </c>
       <c r="G24" s="3">
-        <v>1.3979999999999999</v>
+        <v>1.4079999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1188,7 +1188,7 @@
         <v>45</v>
       </c>
       <c r="B25" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C25" t="s">
         <v>43</v>
@@ -1197,13 +1197,13 @@
         <v>11</v>
       </c>
       <c r="E25" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F25" s="2">
         <v>0.03</v>
       </c>
       <c r="G25" s="3">
-        <v>1.1779999999999999</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1211,7 +1211,7 @@
         <v>46</v>
       </c>
       <c r="B26" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C26" t="s">
         <v>43</v>
@@ -1220,13 +1220,13 @@
         <v>41</v>
       </c>
       <c r="E26" s="2">
-        <v>1.385</v>
+        <v>1.4279999999999999</v>
       </c>
       <c r="F26" s="2">
         <v>0.08</v>
       </c>
       <c r="G26" s="3">
-        <v>1.4650000000000001</v>
+        <v>1.508</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1234,7 +1234,7 @@
         <v>47</v>
       </c>
       <c r="B27" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C27" t="s">
         <v>48</v>
@@ -1243,13 +1243,13 @@
         <v>9</v>
       </c>
       <c r="E27" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F27" s="2">
         <v>0.08</v>
       </c>
       <c r="G27" s="3">
-        <v>1.274</v>
+        <v>1.3169999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1257,7 +1257,7 @@
         <v>49</v>
       </c>
       <c r="B28" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C28" t="s">
         <v>48</v>
@@ -1266,13 +1266,13 @@
         <v>11</v>
       </c>
       <c r="E28" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F28" s="2">
         <v>0.04</v>
       </c>
       <c r="G28" s="3">
-        <v>1.1879999999999999</v>
+        <v>1.238</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1280,7 +1280,7 @@
         <v>50</v>
       </c>
       <c r="B29" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C29" t="s">
         <v>51</v>
@@ -1289,13 +1289,13 @@
         <v>9</v>
       </c>
       <c r="E29" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F29" s="2">
         <v>0.04</v>
       </c>
       <c r="G29" s="3">
-        <v>1.234</v>
+        <v>1.2769999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1303,7 +1303,7 @@
         <v>52</v>
       </c>
       <c r="B30" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C30" t="s">
         <v>51</v>
@@ -1312,13 +1312,13 @@
         <v>11</v>
       </c>
       <c r="E30" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F30" s="2">
         <v>0.02</v>
       </c>
       <c r="G30" s="3">
-        <v>1.1679999999999999</v>
+        <v>1.218</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1326,7 +1326,7 @@
         <v>53</v>
       </c>
       <c r="B31" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C31" t="s">
         <v>54</v>
@@ -1335,13 +1335,13 @@
         <v>9</v>
       </c>
       <c r="E31" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F31" s="2">
         <v>0.06</v>
       </c>
       <c r="G31" s="3">
-        <v>1.254</v>
+        <v>1.2969999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1349,7 +1349,7 @@
         <v>55</v>
       </c>
       <c r="B32" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C32" t="s">
         <v>54</v>
@@ -1358,13 +1358,13 @@
         <v>11</v>
       </c>
       <c r="E32" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F32" s="2">
         <v>0.04</v>
       </c>
       <c r="G32" s="3">
-        <v>1.1879999999999999</v>
+        <v>1.238</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1372,7 +1372,7 @@
         <v>56</v>
       </c>
       <c r="B33" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C33" t="s">
         <v>57</v>
@@ -1381,13 +1381,13 @@
         <v>9</v>
       </c>
       <c r="E33" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F33" s="2">
         <v>0.04</v>
       </c>
       <c r="G33" s="3">
-        <v>1.234</v>
+        <v>1.2769999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1395,7 +1395,7 @@
         <v>58</v>
       </c>
       <c r="B34" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C34" t="s">
         <v>59</v>
@@ -1404,13 +1404,13 @@
         <v>9</v>
       </c>
       <c r="E34" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F34" s="2">
         <v>0.05</v>
       </c>
       <c r="G34" s="3">
-        <v>1.244</v>
+        <v>1.2869999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1418,7 +1418,7 @@
         <v>60</v>
       </c>
       <c r="B35" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C35" t="s">
         <v>59</v>
@@ -1427,13 +1427,13 @@
         <v>11</v>
       </c>
       <c r="E35" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F35" s="2">
         <v>0.02</v>
       </c>
       <c r="G35" s="3">
-        <v>1.1679999999999999</v>
+        <v>1.218</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1441,7 +1441,7 @@
         <v>61</v>
       </c>
       <c r="B36" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C36" t="s">
         <v>62</v>
@@ -1450,13 +1450,13 @@
         <v>9</v>
       </c>
       <c r="E36" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F36" s="2">
         <v>0.04</v>
       </c>
       <c r="G36" s="3">
-        <v>1.234</v>
+        <v>1.2769999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1464,7 +1464,7 @@
         <v>63</v>
       </c>
       <c r="B37" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C37" t="s">
         <v>64</v>
@@ -1473,13 +1473,13 @@
         <v>9</v>
       </c>
       <c r="E37" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F37" s="2">
         <v>0.06</v>
       </c>
       <c r="G37" s="3">
-        <v>1.254</v>
+        <v>1.2969999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1487,7 +1487,7 @@
         <v>65</v>
       </c>
       <c r="B38" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C38" t="s">
         <v>64</v>
@@ -1496,13 +1496,13 @@
         <v>11</v>
       </c>
       <c r="E38" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F38" s="2">
         <v>0.03</v>
       </c>
       <c r="G38" s="3">
-        <v>1.1779999999999999</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1510,7 +1510,7 @@
         <v>66</v>
       </c>
       <c r="B39" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C39" t="s">
         <v>67</v>
@@ -1519,13 +1519,13 @@
         <v>9</v>
       </c>
       <c r="E39" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F39" s="2">
         <v>0.06</v>
       </c>
       <c r="G39" s="3">
-        <v>1.254</v>
+        <v>1.2969999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1533,7 +1533,7 @@
         <v>68</v>
       </c>
       <c r="B40" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C40" t="s">
         <v>67</v>
@@ -1542,13 +1542,13 @@
         <v>38</v>
       </c>
       <c r="E40" s="2">
-        <v>1.3180000000000001</v>
+        <v>1.3280000000000001</v>
       </c>
       <c r="F40" s="2">
         <v>0.08</v>
       </c>
       <c r="G40" s="3">
-        <v>1.3979999999999999</v>
+        <v>1.4079999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1556,7 +1556,7 @@
         <v>69</v>
       </c>
       <c r="B41" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C41" t="s">
         <v>67</v>
@@ -1565,13 +1565,13 @@
         <v>11</v>
       </c>
       <c r="E41" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F41" s="2">
         <v>0.03</v>
       </c>
       <c r="G41" s="3">
-        <v>1.1779999999999999</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1579,7 +1579,7 @@
         <v>70</v>
       </c>
       <c r="B42" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C42" t="s">
         <v>67</v>
@@ -1588,13 +1588,13 @@
         <v>41</v>
       </c>
       <c r="E42" s="2">
-        <v>1.385</v>
+        <v>1.4279999999999999</v>
       </c>
       <c r="F42" s="2">
         <v>0.08</v>
       </c>
       <c r="G42" s="3">
-        <v>1.4650000000000001</v>
+        <v>1.508</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1602,7 +1602,7 @@
         <v>71</v>
       </c>
       <c r="B43" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C43" t="s">
         <v>72</v>
@@ -1611,13 +1611,13 @@
         <v>9</v>
       </c>
       <c r="E43" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F43" s="2">
         <v>0.06</v>
       </c>
       <c r="G43" s="3">
-        <v>1.254</v>
+        <v>1.2969999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1625,7 +1625,7 @@
         <v>73</v>
       </c>
       <c r="B44" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C44" t="s">
         <v>72</v>
@@ -1634,13 +1634,13 @@
         <v>11</v>
       </c>
       <c r="E44" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F44" s="2">
         <v>0.04</v>
       </c>
       <c r="G44" s="3">
-        <v>1.1879999999999999</v>
+        <v>1.238</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1648,7 +1648,7 @@
         <v>74</v>
       </c>
       <c r="B45" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C45" t="s">
         <v>75</v>
@@ -1657,13 +1657,13 @@
         <v>9</v>
       </c>
       <c r="E45" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F45" s="2">
         <v>0.06</v>
       </c>
       <c r="G45" s="3">
-        <v>1.254</v>
+        <v>1.2969999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1671,7 +1671,7 @@
         <v>76</v>
       </c>
       <c r="B46" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C46" t="s">
         <v>75</v>
@@ -1680,13 +1680,13 @@
         <v>38</v>
       </c>
       <c r="E46" s="2">
-        <v>1.3180000000000001</v>
+        <v>1.3280000000000001</v>
       </c>
       <c r="F46" s="2">
         <v>0.08</v>
       </c>
       <c r="G46" s="3">
-        <v>1.3979999999999999</v>
+        <v>1.4079999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1694,7 +1694,7 @@
         <v>77</v>
       </c>
       <c r="B47" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C47" t="s">
         <v>75</v>
@@ -1703,13 +1703,13 @@
         <v>11</v>
       </c>
       <c r="E47" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F47" s="2">
         <v>0.03</v>
       </c>
       <c r="G47" s="3">
-        <v>1.1779999999999999</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1717,7 +1717,7 @@
         <v>78</v>
       </c>
       <c r="B48" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C48" t="s">
         <v>75</v>
@@ -1726,13 +1726,13 @@
         <v>41</v>
       </c>
       <c r="E48" s="2">
-        <v>1.385</v>
+        <v>1.4279999999999999</v>
       </c>
       <c r="F48" s="2">
         <v>0.08</v>
       </c>
       <c r="G48" s="3">
-        <v>1.4650000000000001</v>
+        <v>1.508</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1740,7 +1740,7 @@
         <v>79</v>
       </c>
       <c r="B49" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C49" t="s">
         <v>80</v>
@@ -1749,13 +1749,13 @@
         <v>9</v>
       </c>
       <c r="E49" s="2">
-        <v>1.194</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="F49" s="2">
         <v>0.06</v>
       </c>
       <c r="G49" s="3">
-        <v>1.254</v>
+        <v>1.2969999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1763,7 +1763,7 @@
         <v>81</v>
       </c>
       <c r="B50" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C50" t="s">
         <v>80</v>
@@ -1772,13 +1772,13 @@
         <v>38</v>
       </c>
       <c r="E50" s="2">
-        <v>1.3180000000000001</v>
+        <v>1.3280000000000001</v>
       </c>
       <c r="F50" s="2">
         <v>0.08</v>
       </c>
       <c r="G50" s="3">
-        <v>1.3979999999999999</v>
+        <v>1.4079999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1786,7 +1786,7 @@
         <v>82</v>
       </c>
       <c r="B51" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C51" t="s">
         <v>80</v>
@@ -1795,13 +1795,13 @@
         <v>11</v>
       </c>
       <c r="E51" s="2">
-        <v>1.1479999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="F51" s="2">
         <v>0.03</v>
       </c>
       <c r="G51" s="3">
-        <v>1.1779999999999999</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1809,7 +1809,7 @@
         <v>83</v>
       </c>
       <c r="B52" s="1">
-        <v>46088</v>
+        <v>46090</v>
       </c>
       <c r="C52" t="s">
         <v>80</v>
@@ -1818,13 +1818,13 @@
         <v>41</v>
       </c>
       <c r="E52" s="2">
-        <v>1.385</v>
+        <v>1.4279999999999999</v>
       </c>
       <c r="F52" s="2">
         <v>0.08</v>
       </c>
       <c r="G52" s="3">
-        <v>1.4650000000000001</v>
+        <v>1.508</v>
       </c>
     </row>
   </sheetData>
